--- a/Test/ユーザ登録 単体テスト/ユーザー登録 完了画面単体テストケース.xlsx
+++ b/Test/ユーザ登録 単体テスト/ユーザー登録 完了画面単体テストケース.xlsx
@@ -13,20 +13,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="107">
   <si>
     <t>テストID</t>
   </si>
   <si>
+    <t>観点カテゴリ</t>
+  </si>
+  <si>
+    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
+  </si>
+  <si>
     <t>機能名</t>
   </si>
   <si>
+    <t>チェック項目</t>
+  </si>
+  <si>
     <t>テスト観点・目的</t>
   </si>
   <si>
+    <t>確認済</t>
+  </si>
+  <si>
     <t>前提条件</t>
   </si>
   <si>
+    <t>備考</t>
+  </si>
+  <si>
     <t>テスト手順</t>
   </si>
   <si>
@@ -36,6 +51,9 @@
     <t>期待結果</t>
   </si>
   <si>
+    <t>入力値検証</t>
+  </si>
+  <si>
     <t>優先度</t>
   </si>
   <si>
@@ -51,15 +69,27 @@
     <t>合否判定</t>
   </si>
   <si>
-    <t>備考</t>
+    <t>正常値（代表値）のテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>□</t>
   </si>
   <si>
     <t>UT-001</t>
   </si>
   <si>
+    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
+  </si>
+  <si>
     <t>画面遷移</t>
   </si>
   <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>空文字・Nullのテストケースを作成したか</t>
+  </si>
+  <si>
     <t>ボタンの機能チェック</t>
   </si>
   <si>
@@ -67,6 +97,12 @@
   </si>
   <si>
     <t>登録完了画面に表示された「TOPページへ戻る」ボタンを押す</t>
+  </si>
+  <si>
+    <t>不正な形式・特殊文字のテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>機能動作</t>
   </si>
   <si>
     <t>名前（姓）=ひらがな・漢字・10文字以内
@@ -84,172 +120,139 @@
 （※登録画面にて入力する内容）</t>
   </si>
   <si>
+    <t>説明</t>
+  </si>
+  <si>
     <t>D.I.Blogのトップ画面へ遷移する</t>
   </si>
   <si>
+    <t>正常系の動作確認ケースを作成したか</t>
+  </si>
+  <si>
     <t>高</t>
   </si>
   <si>
+    <t>記載例</t>
+  </si>
+  <si>
+    <t>注意点</t>
+  </si>
+  <si>
+    <t>異常系のエラー処理ケースを作成したか</t>
+  </si>
+  <si>
+    <t>例外処理の確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>各テストケースを一意に識別するID</t>
+  </si>
+  <si>
     <t>山本穂乃花</t>
   </si>
   <si>
     <t>D.I.Blogのトップ画面に遷移した</t>
   </si>
   <si>
+    <t>UT-001, UT-002</t>
+  </si>
+  <si>
     <t>合</t>
   </si>
   <si>
+    <t>画面表示</t>
+  </si>
+  <si>
+    <t>期待する画面遷移のケースを作成したか</t>
+  </si>
+  <si>
+    <t>プロジェクト内で重複しないように採番</t>
+  </si>
+  <si>
     <t>UT-002</t>
   </si>
   <si>
     <t>画面上部の「トップ」を押す</t>
   </si>
   <si>
+    <t>エラーメッセージ表示のケースを作成したか</t>
+  </si>
+  <si>
+    <t>テスト対象の機能やクラス名</t>
+  </si>
+  <si>
+    <t>ログイン認証、ユーザー登録</t>
+  </si>
+  <si>
+    <t>要件定義書・設計書と用語を統一</t>
+  </si>
+  <si>
+    <t>必須項目のバリデーションケースを作成したか</t>
+  </si>
+  <si>
+    <t>何を確認するテストか</t>
+  </si>
+  <si>
+    <t>入力値チェック、正常系動作確認</t>
+  </si>
+  <si>
+    <t>データ処理</t>
+  </si>
+  <si>
+    <t>具体的な検証ポイントを明記</t>
+  </si>
+  <si>
     <t>UT-003</t>
   </si>
   <si>
+    <t>データベース登録・更新のケースを作成したか</t>
+  </si>
+  <si>
     <t>画面上部の「アカウント登録」を押す</t>
   </si>
   <si>
+    <t>テスト実行前に整える条件</t>
+  </si>
+  <si>
+    <t>データベース削除のケースを作成したか</t>
+  </si>
+  <si>
+    <t>ログイン画面が表示されている状態</t>
+  </si>
+  <si>
     <t>入力したデータが保存されていないアカウント登録画面に遷移する</t>
   </si>
   <si>
+    <t>環境設定、データ状態なども記載</t>
+  </si>
+  <si>
     <t>入力した内容が保存されていない状態の登録画面に遷移した</t>
   </si>
   <si>
-    <t>観点カテゴリ</t>
-  </si>
-  <si>
-    <t>チェック項目</t>
-  </si>
-  <si>
-    <t>確認済</t>
-  </si>
-  <si>
-    <t>入力値検証</t>
-  </si>
-  <si>
-    <t>正常値（代表値）のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>□</t>
-  </si>
-  <si>
-    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>空文字・Nullのテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>不正な形式・特殊文字のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>機能動作</t>
-  </si>
-  <si>
-    <t>正常系の動作確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>異常系のエラー処理ケースを作成したか</t>
-  </si>
-  <si>
-    <t>例外処理の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>画面表示</t>
-  </si>
-  <si>
-    <t>期待する画面遷移のケースを作成したか</t>
-  </si>
-  <si>
-    <t>エラーメッセージ表示のケースを作成したか</t>
-  </si>
-  <si>
-    <t>必須項目のバリデーションケースを作成したか</t>
-  </si>
-  <si>
-    <t>データ処理</t>
-  </si>
-  <si>
-    <t>データベース登録・更新のケースを作成したか</t>
-  </si>
-  <si>
-    <t>データベース削除のケースを作成したか</t>
-  </si>
-  <si>
     <t>データ検索・取得のケースを作成したか</t>
   </si>
   <si>
-    <t>権限・認証</t>
-  </si>
-  <si>
-    <t>権限チェックのケースを作成したか</t>
-  </si>
-  <si>
-    <t>ログイン状態の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
-  </si>
-  <si>
-    <t>項目名</t>
-  </si>
-  <si>
-    <t>説明</t>
-  </si>
-  <si>
-    <t>記載例</t>
-  </si>
-  <si>
-    <t>注意点</t>
-  </si>
-  <si>
-    <t>各テストケースを一意に識別するID</t>
-  </si>
-  <si>
-    <t>UT-001, UT-002</t>
-  </si>
-  <si>
-    <t>プロジェクト内で重複しないように採番</t>
-  </si>
-  <si>
-    <t>テスト対象の機能やクラス名</t>
-  </si>
-  <si>
-    <t>ログイン認証、ユーザー登録</t>
-  </si>
-  <si>
-    <t>要件定義書・設計書と用語を統一</t>
-  </si>
-  <si>
-    <t>何を確認するテストか</t>
-  </si>
-  <si>
-    <t>入力値チェック、正常系動作確認</t>
-  </si>
-  <si>
-    <t>具体的な検証ポイントを明記</t>
-  </si>
-  <si>
-    <t>テスト実行前に整える条件</t>
-  </si>
-  <si>
-    <t>ログイン画面が表示されている状態</t>
-  </si>
-  <si>
-    <t>環境設定、データ状態なども記載</t>
-  </si>
-  <si>
     <t>具体的な実行ステップ</t>
+  </si>
+  <si>
+    <t>UT-004</t>
   </si>
   <si>
     <t>1. ユーザーID欄に入力
 2. ボタンをクリック</t>
   </si>
   <si>
+    <t>権限・認証</t>
+  </si>
+  <si>
+    <t>アドレスチェック</t>
+  </si>
+  <si>
     <t>番号付きで誰でも実行できるよう詳細に</t>
   </si>
   <si>
+    <t>権限チェックのケースを作成したか</t>
+  </si>
+  <si>
     <t>テストデータ</t>
   </si>
   <si>
@@ -259,7 +262,18 @@
     <t>ユーザーID=test001</t>
   </si>
   <si>
+    <t>ログイン状態の確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>1．入力したデータが保存されていないアカウント登録画面に遷移する
+2．アドレス欄に「http://localhost/Registration_sample/regist.php」と表示される。</t>
+  </si>
+  <si>
     <t>正常値、境界値、異常値を網羅</t>
+  </si>
+  <si>
+    <t>ユーザ登録画面に遷移し、アドレス欄に「http://localhost/Registration_sample/regist.php
+(見える範囲はlocalhost/Registration_sample/regist.php)」と表示された。</t>
   </si>
   <si>
     <t>成功時に得られるべき出力</t>
@@ -359,16 +373,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="14.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font/>
     <font>
@@ -464,22 +478,22 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
@@ -729,158 +743,197 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="4">
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="8">
         <v>46093.0</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2"/>
+      <c r="J2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="A3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="D3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="8">
         <v>46093.0</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="2"/>
+      <c r="J3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="E4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="8">
         <v>46093.0</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" s="2"/>
+      <c r="J4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="8">
+        <v>46275.0</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -1886,197 +1939,197 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="2"/>
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="B9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="3"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="3"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="2"/>
+      <c r="A11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="2"/>
+      <c r="A12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="2"/>
+      <c r="A13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="A14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="3"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="2"/>
+      <c r="A15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="3"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="2"/>
+      <c r="A16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3081,252 +3134,252 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>58</v>
+      <c r="A3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>61</v>
+      <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>64</v>
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>67</v>
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>70</v>
+      <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>77</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>80</v>
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>83</v>
+      <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>86</v>
+      <c r="A12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>86</v>
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="A14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>86</v>
+      <c r="A15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>95</v>
+      <c r="A16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
